--- a/References/Farm_Yard_Manure/FYM_Estimation.xlsx
+++ b/References/Farm_Yard_Manure/FYM_Estimation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2025/Ghana_Project/SOC Modeling/RothC/Initializing Model/Farm_Yard_Manure/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2025/Ghana_Project/QA1_&amp;_3/Documentation/axam-docs/References/Farm_Yard_Manure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F495C7AE-916D-0444-9F1B-4BBDA14B0268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7196C7C-4A98-C548-BB79-ABD08FF1A649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="220" yWindow="1760" windowWidth="28040" windowHeight="17360" xr2:uid="{9B614686-3E97-1649-841A-2D4C36F2B2B5}"/>
   </bookViews>
